--- a/Registro de Métricas - Kairos - NexTech.xlsx
+++ b/Registro de Métricas - Kairos - NexTech.xlsx
@@ -15,9 +15,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="16">
-  <si>
-    <t xml:space="preserve">Ratio de Ajustes </t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="22">
+  <si>
+    <t>Documentos sin necesidad de ajustes</t>
   </si>
   <si>
     <t>Etapa</t>
@@ -26,15 +26,21 @@
     <t>Trabajo total</t>
   </si>
   <si>
-    <t>ajustes en documento</t>
+    <t>documentos sin ajuste necesario</t>
   </si>
   <si>
     <t>Porcentaje</t>
   </si>
   <si>
+    <t>Porcentaje planificado</t>
+  </si>
+  <si>
     <t>Inicio I-1</t>
   </si>
   <si>
+    <t>no planificado</t>
+  </si>
+  <si>
     <t>Elaboración I-1</t>
   </si>
   <si>
@@ -44,6 +50,12 @@
     <t>Construcción I-1</t>
   </si>
   <si>
+    <t>para esta metrica deberíamos tener planificado un 80%, no un 100%</t>
+  </si>
+  <si>
+    <t>que</t>
+  </si>
+  <si>
     <t>Reuniones</t>
   </si>
   <si>
@@ -60,6 +72,12 @@
   </si>
   <si>
     <t>Revisión de Documentos</t>
+  </si>
+  <si>
+    <t>(no planificado)</t>
+  </si>
+  <si>
+    <t>(tampoco planificado xd)</t>
   </si>
   <si>
     <t>CU X H-H</t>
@@ -99,7 +117,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="4">
     <border/>
     <border>
       <left style="thin">
@@ -115,11 +133,27 @@
         <color rgb="FF000000"/>
       </bottom>
     </border>
+    <border>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+    </border>
+    <border>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="11">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -132,12 +166,19 @@
     <xf borderId="1" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
+    <xf borderId="2" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
     <xf borderId="1" fillId="0" fontId="1" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="2" fillId="0" fontId="1" numFmtId="9" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment readingOrder="0"/>
     </xf>
     <xf borderId="1" fillId="0" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="1" fillId="0" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="1" fillId="0" fontId="1" numFmtId="164" xfId="0" applyBorder="1" applyFont="1" applyNumberFormat="1"/>
+    <xf borderId="3" fillId="0" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle xfId="0" name="Normal" builtinId="0"/>
@@ -367,7 +408,10 @@
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
   <cols>
+    <col customWidth="1" min="1" max="1" width="15.38"/>
+    <col customWidth="1" min="2" max="2" width="14.63"/>
     <col customWidth="1" min="3" max="3" width="44.63"/>
+    <col customWidth="1" min="5" max="5" width="17.63"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -391,10 +435,13 @@
       <c r="D2" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="E2" s="4" t="s">
+        <v>5</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B3" s="3">
         <v>8.0</v>
@@ -406,50 +453,72 @@
         <f t="shared" ref="D3:D6" si="1">C3*100/B3</f>
         <v>50</v>
       </c>
+      <c r="E3" s="4" t="s">
+        <v>7</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B4" s="3">
         <v>11.0</v>
       </c>
       <c r="C4" s="3">
-        <v>4.0</v>
-      </c>
-      <c r="D4" s="4">
+        <v>7.0</v>
+      </c>
+      <c r="D4" s="5">
         <f t="shared" si="1"/>
-        <v>36.36363636</v>
+        <v>63.63636364</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B5" s="3">
         <v>13.0</v>
       </c>
       <c r="C5" s="3">
-        <v>3.0</v>
+        <v>10.0</v>
       </c>
       <c r="D5" s="3">
         <f t="shared" si="1"/>
-        <v>23.07692308</v>
+        <v>76.92307692</v>
+      </c>
+      <c r="E5" s="6">
+        <v>0.8</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B6" s="3">
         <v>6.0</v>
       </c>
       <c r="C6" s="3">
-        <v>0.5</v>
+        <v>5.5</v>
       </c>
       <c r="D6" s="3">
         <f t="shared" si="1"/>
-        <v>8.333333333</v>
+        <v>91.66666667</v>
+      </c>
+      <c r="E6" s="6">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="C8" s="2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="C9" s="2" t="s">
+        <v>12</v>
       </c>
     </row>
   </sheetData>
@@ -466,11 +535,12 @@
   <cols>
     <col customWidth="1" min="1" max="1" width="14.13"/>
     <col customWidth="1" min="3" max="3" width="44.63"/>
+    <col customWidth="1" min="5" max="5" width="18.63"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -481,18 +551,21 @@
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="E2" s="4" t="s">
+        <v>5</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B3" s="3">
         <v>0.0</v>
@@ -500,11 +573,14 @@
       <c r="C3" s="3">
         <v>0.0</v>
       </c>
-      <c r="D3" s="5"/>
+      <c r="D3" s="7"/>
+      <c r="E3" s="4" t="s">
+        <v>7</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B4" s="3">
         <v>3.0</v>
@@ -515,10 +591,13 @@
       <c r="D4" s="3">
         <v>100.0</v>
       </c>
+      <c r="E4" s="6">
+        <v>1.0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B5" s="3">
         <v>5.0</v>
@@ -529,10 +608,13 @@
       <c r="D5" s="3">
         <v>80.0</v>
       </c>
+      <c r="E5" s="6">
+        <v>1.0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B6" s="3">
         <v>2.0</v>
@@ -542,6 +624,9 @@
       </c>
       <c r="D6" s="3">
         <v>50.0</v>
+      </c>
+      <c r="E6" s="6">
+        <v>1.0</v>
       </c>
     </row>
   </sheetData>
@@ -557,11 +642,12 @@
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
   <cols>
     <col customWidth="1" min="3" max="3" width="44.63"/>
+    <col customWidth="1" min="5" max="5" width="18.25"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="2"/>
@@ -569,21 +655,24 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="E2" s="4" t="s">
+        <v>5</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B3" s="3">
         <v>0.0</v>
@@ -591,11 +680,14 @@
       <c r="C3" s="3">
         <v>0.0</v>
       </c>
-      <c r="D3" s="5"/>
+      <c r="D3" s="7"/>
+      <c r="E3" s="4">
+        <v>0.0</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B4" s="3">
         <v>0.0</v>
@@ -603,11 +695,14 @@
       <c r="C4" s="3">
         <v>0.0</v>
       </c>
-      <c r="D4" s="5"/>
+      <c r="D4" s="7"/>
+      <c r="E4" s="4">
+        <v>0.0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B5" s="3">
         <v>2.0</v>
@@ -618,10 +713,13 @@
       <c r="D5" s="3">
         <v>50.0</v>
       </c>
+      <c r="E5" s="6">
+        <v>0.9</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B6" s="3">
         <v>2.0</v>
@@ -631,6 +729,9 @@
       </c>
       <c r="D6" s="3">
         <v>50.0</v>
+      </c>
+      <c r="E6" s="6">
+        <v>0.9</v>
       </c>
     </row>
   </sheetData>
@@ -646,11 +747,13 @@
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
   <cols>
     <col customWidth="1" min="3" max="3" width="44.63"/>
+    <col customWidth="1" min="5" max="5" width="17.88"/>
+    <col customWidth="1" min="6" max="6" width="21.5"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="2"/>
@@ -661,18 +764,21 @@
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="E2" s="4" t="s">
+        <v>5</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B3" s="3">
         <v>5.0</v>
@@ -680,14 +786,20 @@
       <c r="C3" s="3">
         <v>3.0</v>
       </c>
-      <c r="D3" s="6">
+      <c r="D3" s="8">
         <f t="shared" ref="D3:D5" si="1">C3*100/B3</f>
         <v>60</v>
       </c>
+      <c r="E3" s="6">
+        <v>0.7</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>19</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B4" s="3">
         <v>7.0</v>
@@ -695,30 +807,41 @@
       <c r="C4" s="3">
         <v>5.0</v>
       </c>
-      <c r="D4" s="7">
+      <c r="D4" s="9">
         <f t="shared" si="1"/>
         <v>71.42857143</v>
       </c>
+      <c r="E4" s="6">
+        <v>0.8</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>20</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B5" s="3">
         <v>4.0</v>
       </c>
       <c r="C5" s="3">
-        <v>1.0</v>
-      </c>
-      <c r="D5" s="5">
+        <v>2.0</v>
+      </c>
+      <c r="D5" s="7">
         <f t="shared" si="1"/>
-        <v>25</v>
+        <v>50</v>
+      </c>
+      <c r="E5" s="6">
+        <v>0.9</v>
       </c>
     </row>
     <row r="6">
-      <c r="B6" s="5"/>
-      <c r="C6" s="5"/>
-      <c r="D6" s="5"/>
+      <c r="A6" s="10"/>
+      <c r="B6" s="7"/>
+      <c r="C6" s="7"/>
+      <c r="D6" s="7"/>
+      <c r="E6" s="6"/>
     </row>
   </sheetData>
   <drawing r:id="rId1"/>
@@ -734,7 +857,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -745,10 +868,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>4</v>
@@ -756,7 +879,7 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B3" s="3">
         <v>0.0</v>
@@ -770,7 +893,7 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B4" s="3">
         <v>0.0</v>
@@ -778,13 +901,13 @@
       <c r="C4" s="3">
         <v>0.0</v>
       </c>
-      <c r="D4" s="4">
+      <c r="D4" s="5">
         <v>0.0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B5" s="3">
         <v>0.0</v>

--- a/Registro de Métricas - Kairos - NexTech.xlsx
+++ b/Registro de Métricas - Kairos - NexTech.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="21">
   <si>
     <t>Documentos sin necesidad de ajustes</t>
   </si>
@@ -53,9 +53,6 @@
     <t>para esta metrica deberíamos tener planificado un 80%, no un 100%</t>
   </si>
   <si>
-    <t>que</t>
-  </si>
-  <si>
     <t>Reuniones</t>
   </si>
   <si>
@@ -65,7 +62,7 @@
     <t>Realizadas</t>
   </si>
   <si>
-    <t>Revisi+on Técnica Formal RTF</t>
+    <t>Revisión Técnica Formal RTF</t>
   </si>
   <si>
     <t>Etiqueta</t>
@@ -153,7 +150,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -174,6 +171,9 @@
     </xf>
     <xf borderId="2" fillId="0" fontId="1" numFmtId="9" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" wrapText="1"/>
     </xf>
     <xf borderId="1" fillId="0" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="1" fillId="0" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
@@ -410,7 +410,7 @@
   <cols>
     <col customWidth="1" min="1" max="1" width="15.38"/>
     <col customWidth="1" min="2" max="2" width="14.63"/>
-    <col customWidth="1" min="3" max="3" width="44.63"/>
+    <col customWidth="1" min="3" max="3" width="26.25"/>
     <col customWidth="1" min="5" max="5" width="17.63"/>
   </cols>
   <sheetData>
@@ -501,24 +501,19 @@
         <v>6.0</v>
       </c>
       <c r="C6" s="3">
-        <v>5.5</v>
+        <v>4.0</v>
       </c>
       <c r="D6" s="3">
         <f t="shared" si="1"/>
-        <v>91.66666667</v>
+        <v>66.66666667</v>
       </c>
       <c r="E6" s="6">
         <v>0.8</v>
       </c>
     </row>
     <row r="8">
-      <c r="C8" s="2" t="s">
+      <c r="C8" s="7" t="s">
         <v>11</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="C9" s="2" t="s">
-        <v>12</v>
       </c>
     </row>
   </sheetData>
@@ -540,7 +535,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -551,10 +546,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" s="3" t="s">
         <v>14</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>15</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>4</v>
@@ -573,7 +568,7 @@
       <c r="C3" s="3">
         <v>0.0</v>
       </c>
-      <c r="D3" s="7"/>
+      <c r="D3" s="8"/>
       <c r="E3" s="4" t="s">
         <v>7</v>
       </c>
@@ -620,10 +615,11 @@
         <v>2.0</v>
       </c>
       <c r="C6" s="3">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="D6" s="3">
-        <v>50.0</v>
+        <f>C6*100/B6</f>
+        <v>100</v>
       </c>
       <c r="E6" s="6">
         <v>1.0</v>
@@ -641,13 +637,16 @@
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
   <cols>
-    <col customWidth="1" min="3" max="3" width="44.63"/>
+    <col customWidth="1" min="1" max="1" width="15.38"/>
+    <col customWidth="1" min="2" max="2" width="9.38"/>
+    <col customWidth="1" min="3" max="3" width="10.88"/>
+    <col customWidth="1" min="4" max="4" width="10.38"/>
     <col customWidth="1" min="5" max="5" width="18.25"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="2"/>
@@ -655,13 +654,13 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B2" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" s="3" t="s">
         <v>14</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>15</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>4</v>
@@ -680,7 +679,7 @@
       <c r="C3" s="3">
         <v>0.0</v>
       </c>
-      <c r="D3" s="7"/>
+      <c r="D3" s="8"/>
       <c r="E3" s="4">
         <v>0.0</v>
       </c>
@@ -695,7 +694,7 @@
       <c r="C4" s="3">
         <v>0.0</v>
       </c>
-      <c r="D4" s="7"/>
+      <c r="D4" s="8"/>
       <c r="E4" s="4">
         <v>0.0</v>
       </c>
@@ -713,9 +712,7 @@
       <c r="D5" s="3">
         <v>50.0</v>
       </c>
-      <c r="E5" s="6">
-        <v>0.9</v>
-      </c>
+      <c r="E5" s="6"/>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
@@ -725,14 +722,13 @@
         <v>2.0</v>
       </c>
       <c r="C6" s="3">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="D6" s="3">
-        <v>50.0</v>
-      </c>
-      <c r="E6" s="6">
-        <v>0.9</v>
-      </c>
+        <f>C6*100/B6</f>
+        <v>150</v>
+      </c>
+      <c r="E6" s="6"/>
     </row>
   </sheetData>
   <drawing r:id="rId1"/>
@@ -746,14 +742,14 @@
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
   <cols>
-    <col customWidth="1" min="3" max="3" width="44.63"/>
+    <col customWidth="1" min="3" max="3" width="12.25"/>
     <col customWidth="1" min="5" max="5" width="17.88"/>
     <col customWidth="1" min="6" max="6" width="21.5"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="2"/>
@@ -764,10 +760,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" s="3" t="s">
         <v>14</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>15</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>4</v>
@@ -786,7 +782,7 @@
       <c r="C3" s="3">
         <v>3.0</v>
       </c>
-      <c r="D3" s="8">
+      <c r="D3" s="9">
         <f t="shared" ref="D3:D5" si="1">C3*100/B3</f>
         <v>60</v>
       </c>
@@ -794,7 +790,7 @@
         <v>0.7</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="4">
@@ -807,7 +803,7 @@
       <c r="C4" s="3">
         <v>5.0</v>
       </c>
-      <c r="D4" s="9">
+      <c r="D4" s="10">
         <f t="shared" si="1"/>
         <v>71.42857143</v>
       </c>
@@ -815,7 +811,7 @@
         <v>0.8</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="5">
@@ -826,21 +822,21 @@
         <v>4.0</v>
       </c>
       <c r="C5" s="3">
-        <v>2.0</v>
-      </c>
-      <c r="D5" s="7">
+        <v>5.0</v>
+      </c>
+      <c r="D5" s="8">
         <f t="shared" si="1"/>
-        <v>50</v>
+        <v>125</v>
       </c>
       <c r="E5" s="6">
         <v>0.9</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="10"/>
-      <c r="B6" s="7"/>
-      <c r="C6" s="7"/>
-      <c r="D6" s="7"/>
+      <c r="A6" s="11"/>
+      <c r="B6" s="8"/>
+      <c r="C6" s="8"/>
+      <c r="D6" s="8"/>
       <c r="E6" s="6"/>
     </row>
   </sheetData>
@@ -857,7 +853,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -868,10 +864,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" s="3" t="s">
         <v>14</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>15</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>4</v>

--- a/Registro de Métricas - Kairos - NexTech.xlsx
+++ b/Registro de Métricas - Kairos - NexTech.xlsx
@@ -656,7 +656,7 @@
         <v>2.0</v>
       </c>
       <c r="G11" s="4">
-        <f>F11*100/E11</f>
+        <f t="shared" ref="G11:G12" si="1">F11*100/E11</f>
         <v>100</v>
       </c>
     </row>
@@ -664,9 +664,16 @@
       <c r="D12" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="E12" s="4"/>
-      <c r="F12" s="4"/>
-      <c r="G12" s="4"/>
+      <c r="E12" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="F12" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="G12" s="4">
+        <f t="shared" si="1"/>
+        <v>100</v>
+      </c>
     </row>
     <row r="13">
       <c r="D13" s="10" t="s">
@@ -727,7 +734,7 @@
         <v>3.0</v>
       </c>
       <c r="G8" s="14">
-        <f t="shared" ref="G8:G10" si="1">F8*100/E8</f>
+        <f t="shared" ref="G8:G11" si="1">F8*100/E8</f>
         <v>60</v>
       </c>
     </row>
@@ -765,9 +772,16 @@
       <c r="D11" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="E11" s="5"/>
-      <c r="F11" s="5"/>
-      <c r="G11" s="5"/>
+      <c r="E11" s="4">
+        <v>12.0</v>
+      </c>
+      <c r="F11" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="G11" s="5">
+        <f t="shared" si="1"/>
+        <v>8.333333333</v>
+      </c>
     </row>
     <row r="12">
       <c r="D12" s="13" t="s">

--- a/Registro de Métricas - Kairos - NexTech.xlsx
+++ b/Registro de Métricas - Kairos - NexTech.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="22">
   <si>
     <t>RTF</t>
   </si>
@@ -62,7 +62,25 @@
     <t>Documentos sin ajuste</t>
   </si>
   <si>
-    <t>CU X H-H</t>
+    <t>H-H x PCUa</t>
+  </si>
+  <si>
+    <t>CU implementados</t>
+  </si>
+  <si>
+    <t>PCU ajustados</t>
+  </si>
+  <si>
+    <t>Horas Hombre</t>
+  </si>
+  <si>
+    <t>hh x pcua</t>
+  </si>
+  <si>
+    <t>01, 09, 12, 20</t>
+  </si>
+  <si>
+    <t>07,08,13, 14, 15, 16, 21</t>
   </si>
 </sst>
 </file>
@@ -96,7 +114,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="11">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -151,12 +169,6 @@
         <bgColor rgb="FF9FC5E8"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF4CCCC"/>
-        <bgColor rgb="FFF4CCCC"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="2">
     <border/>
@@ -178,7 +190,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="22">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -231,8 +243,11 @@
     <xf borderId="1" fillId="0" fontId="2" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="0" fillId="10" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
-      <alignment readingOrder="0"/>
+    <xf borderId="1" fillId="8" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" vertical="center"/>
+    </xf>
+    <xf borderId="1" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -545,7 +560,9 @@
       <c r="D12" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="E12" s="4"/>
+      <c r="E12" s="4">
+        <v>4.0</v>
+      </c>
       <c r="F12" s="4"/>
       <c r="G12" s="4"/>
     </row>
@@ -847,7 +864,7 @@
         <v>4.0</v>
       </c>
       <c r="G8" s="4">
-        <f t="shared" ref="G8:G11" si="1">F8*100/E8</f>
+        <f t="shared" ref="G8:G12" si="1">F8*100/E8</f>
         <v>50</v>
       </c>
     </row>
@@ -900,9 +917,16 @@
       <c r="D12" s="18" t="s">
         <v>9</v>
       </c>
-      <c r="E12" s="4"/>
-      <c r="F12" s="4"/>
-      <c r="G12" s="4"/>
+      <c r="E12" s="4">
+        <v>12.0</v>
+      </c>
+      <c r="F12" s="4">
+        <v>12.0</v>
+      </c>
+      <c r="G12" s="4">
+        <f t="shared" si="1"/>
+        <v>100</v>
+      </c>
     </row>
     <row r="13">
       <c r="D13" s="18" t="s">
@@ -927,91 +951,73 @@
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="14.25"/>
-    <col customWidth="1" min="2" max="3" width="10.0"/>
+    <col customWidth="1" min="5" max="6" width="14.38"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="20" t="s">
+    <row r="4">
+      <c r="D4" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="B1" s="7"/>
-      <c r="C1" s="7"/>
-      <c r="D1" s="7"/>
-    </row>
-    <row r="2">
-      <c r="A2" s="4" t="s">
+    </row>
+    <row r="7">
+      <c r="D7" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="B2" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="C2" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="D2" s="4" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="B3" s="4">
-        <v>0.0</v>
-      </c>
-      <c r="C3" s="4">
-        <v>0.0</v>
-      </c>
-      <c r="D3" s="4">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="B4" s="4">
-        <v>0.0</v>
-      </c>
-      <c r="C4" s="4">
-        <v>0.0</v>
-      </c>
-      <c r="D4" s="19">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="4" t="s">
+      <c r="E7" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="F7" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="G7" s="17" t="s">
+        <v>18</v>
+      </c>
+      <c r="H7" s="17" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="D8" s="18" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="4">
-        <v>0.0</v>
-      </c>
-      <c r="C5" s="4">
-        <v>0.0</v>
-      </c>
-      <c r="D5" s="4">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="4" t="s">
+      <c r="E8" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="F8" s="4">
+        <v>43.1</v>
+      </c>
+      <c r="G8" s="4">
+        <v>67.0</v>
+      </c>
+      <c r="H8" s="4">
+        <f>G8/F8</f>
+        <v>1.554524362</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="D9" s="20" t="s">
         <v>9</v>
       </c>
-      <c r="B6" s="4"/>
-      <c r="C6" s="4"/>
-      <c r="D6" s="4"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="4" t="s">
+      <c r="E9" s="21" t="s">
+        <v>21</v>
+      </c>
+      <c r="F9" s="4"/>
+      <c r="G9" s="4"/>
+      <c r="H9" s="4"/>
+    </row>
+    <row r="10">
+      <c r="D10" s="18" t="s">
         <v>10</v>
       </c>
-      <c r="B7" s="4"/>
-      <c r="C7" s="4"/>
-      <c r="D7" s="4"/>
+      <c r="E10" s="4"/>
+      <c r="F10" s="4"/>
+      <c r="G10" s="4"/>
+      <c r="H10" s="4"/>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="D4:H5"/>
+  </mergeCells>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/Registro de Métricas - Kairos - NexTech.xlsx
+++ b/Registro de Métricas - Kairos - NexTech.xlsx
@@ -793,11 +793,11 @@
         <v>12.0</v>
       </c>
       <c r="F11" s="4">
-        <v>1.0</v>
+        <v>8.0</v>
       </c>
       <c r="G11" s="5">
         <f t="shared" si="1"/>
-        <v>8.333333333</v>
+        <v>66.66666667</v>
       </c>
     </row>
     <row r="12">

--- a/Registro de Métricas - Kairos - NexTech.xlsx
+++ b/Registro de Métricas - Kairos - NexTech.xlsx
@@ -552,7 +552,7 @@
         <v>3.0</v>
       </c>
       <c r="G11" s="4">
-        <f>F11*100/E11</f>
+        <f t="shared" ref="G11:G12" si="1">F11*100/E11</f>
         <v>150</v>
       </c>
     </row>
@@ -563,8 +563,13 @@
       <c r="E12" s="4">
         <v>4.0</v>
       </c>
-      <c r="F12" s="4"/>
-      <c r="G12" s="4"/>
+      <c r="F12" s="4">
+        <v>4.0</v>
+      </c>
+      <c r="G12" s="4">
+        <f t="shared" si="1"/>
+        <v>100</v>
+      </c>
     </row>
     <row r="13">
       <c r="D13" s="3" t="s">
@@ -685,11 +690,11 @@
         <v>1.0</v>
       </c>
       <c r="F12" s="4">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="G12" s="4">
         <f t="shared" si="1"/>
-        <v>100</v>
+        <v>200</v>
       </c>
     </row>
     <row r="13">
@@ -793,11 +798,11 @@
         <v>12.0</v>
       </c>
       <c r="F11" s="4">
-        <v>8.0</v>
+        <v>12.0</v>
       </c>
       <c r="G11" s="5">
         <f t="shared" si="1"/>
-        <v>66.66666667</v>
+        <v>100</v>
       </c>
     </row>
     <row r="12">
@@ -990,7 +995,7 @@
         <v>67.0</v>
       </c>
       <c r="H8" s="4">
-        <f>G8/F8</f>
+        <f t="shared" ref="H8:H9" si="1">G8/F8</f>
         <v>1.554524362</v>
       </c>
     </row>
@@ -1001,9 +1006,17 @@
       <c r="E9" s="21" t="s">
         <v>21</v>
       </c>
-      <c r="F9" s="4"/>
-      <c r="G9" s="4"/>
-      <c r="H9" s="4"/>
+      <c r="F9" s="4">
+        <f>49.6+F8</f>
+        <v>92.7</v>
+      </c>
+      <c r="G9" s="4">
+        <v>112.0</v>
+      </c>
+      <c r="H9" s="4">
+        <f t="shared" si="1"/>
+        <v>1.20819849</v>
+      </c>
     </row>
     <row r="10">
       <c r="D10" s="18" t="s">
